--- a/test_vk12.xlsx
+++ b/test_vk12.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t xml:space="preserve">MATERIAL</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">mat_orgvent_candistr</t>
   </si>
   <si>
-    <t xml:space="preserve">010101001</t>
+    <t xml:space="preserve">ZDET</t>
   </si>
   <si>
     <t xml:space="preserve">orgvent_candistr_gpoart</t>
@@ -68,16 +68,10 @@
     <t xml:space="preserve">orgvent_candistr_sec_ramo_mat</t>
   </si>
   <si>
-    <t xml:space="preserve">010101002</t>
+    <t xml:space="preserve">ZPRO</t>
   </si>
   <si>
     <t xml:space="preserve">orgven_candist_sec_gpoart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZDET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZPRO</t>
   </si>
   <si>
     <t xml:space="preserve">ZCOL</t>
@@ -166,7 +160,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -176,6 +170,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -306,7 +304,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.42"/>
@@ -339,10 +337,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -354,7 +352,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1000</v>
@@ -362,16 +360,20 @@
       <c r="F2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>10002345</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="C3" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1000</v>
@@ -379,56 +381,4056 @@
       <c r="F3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>12</v>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>10003242</v>
+        <v>10006845</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>40</v>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>10</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>10012385</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>14</v>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>40</v>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>10</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+    </row>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+    </row>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+    </row>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+    </row>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+    </row>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+    </row>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+    </row>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+    </row>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+    </row>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+    </row>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+    </row>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+    </row>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+    </row>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+    </row>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+    </row>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+    </row>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+    </row>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+    </row>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+    </row>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+    </row>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+    </row>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+    </row>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+    </row>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+    </row>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+    </row>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+    </row>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+    </row>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+    </row>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+    </row>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+    </row>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+    </row>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+    </row>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+    </row>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+    </row>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+    </row>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+    </row>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+    </row>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+    </row>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+    </row>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+    </row>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+    </row>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+    </row>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+    </row>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+    </row>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+    </row>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+    </row>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H168" s="3"/>
+      <c r="I168" s="3"/>
+    </row>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H169" s="3"/>
+      <c r="I169" s="3"/>
+    </row>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H170" s="3"/>
+      <c r="I170" s="3"/>
+    </row>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H171" s="3"/>
+      <c r="I171" s="3"/>
+    </row>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H172" s="3"/>
+      <c r="I172" s="3"/>
+    </row>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+    </row>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+    </row>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+    </row>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H176" s="3"/>
+      <c r="I176" s="3"/>
+    </row>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H177" s="3"/>
+      <c r="I177" s="3"/>
+    </row>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H178" s="3"/>
+      <c r="I178" s="3"/>
+    </row>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+    </row>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H180" s="3"/>
+      <c r="I180" s="3"/>
+    </row>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+    </row>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+    </row>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+    </row>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+    </row>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+    </row>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+    </row>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+    </row>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+    </row>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+    </row>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H190" s="3"/>
+      <c r="I190" s="3"/>
+    </row>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+    </row>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+    </row>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H193" s="3"/>
+      <c r="I193" s="3"/>
+    </row>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H194" s="3"/>
+      <c r="I194" s="3"/>
+    </row>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H195" s="3"/>
+      <c r="I195" s="3"/>
+    </row>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H196" s="3"/>
+      <c r="I196" s="3"/>
+    </row>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H197" s="3"/>
+      <c r="I197" s="3"/>
+    </row>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H198" s="3"/>
+      <c r="I198" s="3"/>
+    </row>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H199" s="3"/>
+      <c r="I199" s="3"/>
+    </row>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H200" s="3"/>
+      <c r="I200" s="3"/>
+    </row>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H201" s="3"/>
+      <c r="I201" s="3"/>
+    </row>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H202" s="3"/>
+      <c r="I202" s="3"/>
+    </row>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H203" s="3"/>
+      <c r="I203" s="3"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H204" s="3"/>
+      <c r="I204" s="3"/>
+    </row>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H205" s="3"/>
+      <c r="I205" s="3"/>
+    </row>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H206" s="3"/>
+      <c r="I206" s="3"/>
+    </row>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H207" s="3"/>
+      <c r="I207" s="3"/>
+    </row>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H208" s="3"/>
+      <c r="I208" s="3"/>
+    </row>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H209" s="3"/>
+      <c r="I209" s="3"/>
+    </row>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H210" s="3"/>
+      <c r="I210" s="3"/>
+    </row>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H211" s="3"/>
+      <c r="I211" s="3"/>
+    </row>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H212" s="3"/>
+      <c r="I212" s="3"/>
+    </row>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H213" s="3"/>
+      <c r="I213" s="3"/>
+    </row>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
+    </row>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H215" s="3"/>
+      <c r="I215" s="3"/>
+    </row>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H216" s="3"/>
+      <c r="I216" s="3"/>
+    </row>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H217" s="3"/>
+      <c r="I217" s="3"/>
+    </row>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H218" s="3"/>
+      <c r="I218" s="3"/>
+    </row>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H219" s="3"/>
+      <c r="I219" s="3"/>
+    </row>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H220" s="3"/>
+      <c r="I220" s="3"/>
+    </row>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H221" s="3"/>
+      <c r="I221" s="3"/>
+    </row>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H222" s="3"/>
+      <c r="I222" s="3"/>
+    </row>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H223" s="3"/>
+      <c r="I223" s="3"/>
+    </row>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H224" s="3"/>
+      <c r="I224" s="3"/>
+    </row>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H225" s="3"/>
+      <c r="I225" s="3"/>
+    </row>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H226" s="3"/>
+      <c r="I226" s="3"/>
+    </row>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H227" s="3"/>
+      <c r="I227" s="3"/>
+    </row>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H228" s="3"/>
+      <c r="I228" s="3"/>
+    </row>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H229" s="3"/>
+      <c r="I229" s="3"/>
+    </row>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H230" s="3"/>
+      <c r="I230" s="3"/>
+    </row>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H231" s="3"/>
+      <c r="I231" s="3"/>
+    </row>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H232" s="3"/>
+      <c r="I232" s="3"/>
+    </row>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H233" s="3"/>
+      <c r="I233" s="3"/>
+    </row>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H234" s="3"/>
+      <c r="I234" s="3"/>
+    </row>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H235" s="3"/>
+      <c r="I235" s="3"/>
+    </row>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H236" s="3"/>
+      <c r="I236" s="3"/>
+    </row>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H237" s="3"/>
+      <c r="I237" s="3"/>
+    </row>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H238" s="3"/>
+      <c r="I238" s="3"/>
+    </row>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H239" s="3"/>
+      <c r="I239" s="3"/>
+    </row>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H240" s="3"/>
+      <c r="I240" s="3"/>
+    </row>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H241" s="3"/>
+      <c r="I241" s="3"/>
+    </row>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H242" s="3"/>
+      <c r="I242" s="3"/>
+    </row>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H243" s="3"/>
+      <c r="I243" s="3"/>
+    </row>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H244" s="3"/>
+      <c r="I244" s="3"/>
+    </row>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H245" s="3"/>
+      <c r="I245" s="3"/>
+    </row>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H246" s="3"/>
+      <c r="I246" s="3"/>
+    </row>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H247" s="3"/>
+      <c r="I247" s="3"/>
+    </row>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H248" s="3"/>
+      <c r="I248" s="3"/>
+    </row>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H249" s="3"/>
+      <c r="I249" s="3"/>
+    </row>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H250" s="3"/>
+      <c r="I250" s="3"/>
+    </row>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H251" s="3"/>
+      <c r="I251" s="3"/>
+    </row>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H252" s="3"/>
+      <c r="I252" s="3"/>
+    </row>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H253" s="3"/>
+      <c r="I253" s="3"/>
+    </row>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H254" s="3"/>
+      <c r="I254" s="3"/>
+    </row>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H255" s="3"/>
+      <c r="I255" s="3"/>
+    </row>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H256" s="3"/>
+      <c r="I256" s="3"/>
+    </row>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H257" s="3"/>
+      <c r="I257" s="3"/>
+    </row>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H258" s="3"/>
+      <c r="I258" s="3"/>
+    </row>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H259" s="3"/>
+      <c r="I259" s="3"/>
+    </row>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H260" s="3"/>
+      <c r="I260" s="3"/>
+    </row>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H261" s="3"/>
+      <c r="I261" s="3"/>
+    </row>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H262" s="3"/>
+      <c r="I262" s="3"/>
+    </row>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H263" s="3"/>
+      <c r="I263" s="3"/>
+    </row>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H264" s="3"/>
+      <c r="I264" s="3"/>
+    </row>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H265" s="3"/>
+      <c r="I265" s="3"/>
+    </row>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H266" s="3"/>
+      <c r="I266" s="3"/>
+    </row>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H267" s="3"/>
+      <c r="I267" s="3"/>
+    </row>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H268" s="3"/>
+      <c r="I268" s="3"/>
+    </row>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H269" s="3"/>
+      <c r="I269" s="3"/>
+    </row>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H270" s="3"/>
+      <c r="I270" s="3"/>
+    </row>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H271" s="3"/>
+      <c r="I271" s="3"/>
+    </row>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H272" s="3"/>
+      <c r="I272" s="3"/>
+    </row>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H273" s="3"/>
+      <c r="I273" s="3"/>
+    </row>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H274" s="3"/>
+      <c r="I274" s="3"/>
+    </row>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H275" s="3"/>
+      <c r="I275" s="3"/>
+    </row>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H276" s="3"/>
+      <c r="I276" s="3"/>
+    </row>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H277" s="3"/>
+      <c r="I277" s="3"/>
+    </row>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H278" s="3"/>
+      <c r="I278" s="3"/>
+    </row>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H279" s="3"/>
+      <c r="I279" s="3"/>
+    </row>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H280" s="3"/>
+      <c r="I280" s="3"/>
+    </row>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H281" s="3"/>
+      <c r="I281" s="3"/>
+    </row>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H282" s="3"/>
+      <c r="I282" s="3"/>
+    </row>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H283" s="3"/>
+      <c r="I283" s="3"/>
+    </row>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H284" s="3"/>
+      <c r="I284" s="3"/>
+    </row>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H285" s="3"/>
+      <c r="I285" s="3"/>
+    </row>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H286" s="3"/>
+      <c r="I286" s="3"/>
+    </row>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H287" s="3"/>
+      <c r="I287" s="3"/>
+    </row>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H288" s="3"/>
+      <c r="I288" s="3"/>
+    </row>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H289" s="3"/>
+      <c r="I289" s="3"/>
+    </row>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H290" s="3"/>
+      <c r="I290" s="3"/>
+    </row>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H291" s="3"/>
+      <c r="I291" s="3"/>
+    </row>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H292" s="3"/>
+      <c r="I292" s="3"/>
+    </row>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H293" s="3"/>
+      <c r="I293" s="3"/>
+    </row>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H294" s="3"/>
+      <c r="I294" s="3"/>
+    </row>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H295" s="3"/>
+      <c r="I295" s="3"/>
+    </row>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H296" s="3"/>
+      <c r="I296" s="3"/>
+    </row>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H297" s="3"/>
+      <c r="I297" s="3"/>
+    </row>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+    </row>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H299" s="3"/>
+      <c r="I299" s="3"/>
+    </row>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H300" s="3"/>
+      <c r="I300" s="3"/>
+    </row>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H301" s="3"/>
+      <c r="I301" s="3"/>
+    </row>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H302" s="3"/>
+      <c r="I302" s="3"/>
+    </row>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H303" s="3"/>
+      <c r="I303" s="3"/>
+    </row>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+    </row>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H305" s="3"/>
+      <c r="I305" s="3"/>
+    </row>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+    </row>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H307" s="3"/>
+      <c r="I307" s="3"/>
+    </row>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H308" s="3"/>
+      <c r="I308" s="3"/>
+    </row>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H309" s="3"/>
+      <c r="I309" s="3"/>
+    </row>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H310" s="3"/>
+      <c r="I310" s="3"/>
+    </row>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H311" s="3"/>
+      <c r="I311" s="3"/>
+    </row>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H312" s="3"/>
+      <c r="I312" s="3"/>
+    </row>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H313" s="3"/>
+      <c r="I313" s="3"/>
+    </row>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H314" s="3"/>
+      <c r="I314" s="3"/>
+    </row>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H315" s="3"/>
+      <c r="I315" s="3"/>
+    </row>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H316" s="3"/>
+      <c r="I316" s="3"/>
+    </row>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H317" s="3"/>
+      <c r="I317" s="3"/>
+    </row>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H318" s="3"/>
+      <c r="I318" s="3"/>
+    </row>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H319" s="3"/>
+      <c r="I319" s="3"/>
+    </row>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H320" s="3"/>
+      <c r="I320" s="3"/>
+    </row>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H321" s="3"/>
+      <c r="I321" s="3"/>
+    </row>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H322" s="3"/>
+      <c r="I322" s="3"/>
+    </row>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H323" s="3"/>
+      <c r="I323" s="3"/>
+    </row>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H324" s="3"/>
+      <c r="I324" s="3"/>
+    </row>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H325" s="3"/>
+      <c r="I325" s="3"/>
+    </row>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H326" s="3"/>
+      <c r="I326" s="3"/>
+    </row>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H327" s="3"/>
+      <c r="I327" s="3"/>
+    </row>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H328" s="3"/>
+      <c r="I328" s="3"/>
+    </row>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H329" s="3"/>
+      <c r="I329" s="3"/>
+    </row>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H330" s="3"/>
+      <c r="I330" s="3"/>
+    </row>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H331" s="3"/>
+      <c r="I331" s="3"/>
+    </row>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H332" s="3"/>
+      <c r="I332" s="3"/>
+    </row>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H333" s="3"/>
+      <c r="I333" s="3"/>
+    </row>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H334" s="3"/>
+      <c r="I334" s="3"/>
+    </row>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H335" s="3"/>
+      <c r="I335" s="3"/>
+    </row>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H336" s="3"/>
+      <c r="I336" s="3"/>
+    </row>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H337" s="3"/>
+      <c r="I337" s="3"/>
+    </row>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H338" s="3"/>
+      <c r="I338" s="3"/>
+    </row>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H339" s="3"/>
+      <c r="I339" s="3"/>
+    </row>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H340" s="3"/>
+      <c r="I340" s="3"/>
+    </row>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H341" s="3"/>
+      <c r="I341" s="3"/>
+    </row>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H342" s="3"/>
+      <c r="I342" s="3"/>
+    </row>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H343" s="3"/>
+      <c r="I343" s="3"/>
+    </row>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H344" s="3"/>
+      <c r="I344" s="3"/>
+    </row>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H345" s="3"/>
+      <c r="I345" s="3"/>
+    </row>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H346" s="3"/>
+      <c r="I346" s="3"/>
+    </row>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H347" s="3"/>
+      <c r="I347" s="3"/>
+    </row>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H348" s="3"/>
+      <c r="I348" s="3"/>
+    </row>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H349" s="3"/>
+      <c r="I349" s="3"/>
+    </row>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H350" s="3"/>
+      <c r="I350" s="3"/>
+    </row>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H351" s="3"/>
+      <c r="I351" s="3"/>
+    </row>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H352" s="3"/>
+      <c r="I352" s="3"/>
+    </row>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H353" s="3"/>
+      <c r="I353" s="3"/>
+    </row>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H354" s="3"/>
+      <c r="I354" s="3"/>
+    </row>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H355" s="3"/>
+      <c r="I355" s="3"/>
+    </row>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H356" s="3"/>
+      <c r="I356" s="3"/>
+    </row>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H357" s="3"/>
+      <c r="I357" s="3"/>
+    </row>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H358" s="3"/>
+      <c r="I358" s="3"/>
+    </row>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H359" s="3"/>
+      <c r="I359" s="3"/>
+    </row>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H360" s="3"/>
+      <c r="I360" s="3"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H361" s="3"/>
+      <c r="I361" s="3"/>
+    </row>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H362" s="3"/>
+      <c r="I362" s="3"/>
+    </row>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H363" s="3"/>
+      <c r="I363" s="3"/>
+    </row>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H364" s="3"/>
+      <c r="I364" s="3"/>
+    </row>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H365" s="3"/>
+      <c r="I365" s="3"/>
+    </row>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H366" s="3"/>
+      <c r="I366" s="3"/>
+    </row>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H367" s="3"/>
+      <c r="I367" s="3"/>
+    </row>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H368" s="3"/>
+      <c r="I368" s="3"/>
+    </row>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H369" s="3"/>
+      <c r="I369" s="3"/>
+    </row>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H370" s="3"/>
+      <c r="I370" s="3"/>
+    </row>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H371" s="3"/>
+      <c r="I371" s="3"/>
+    </row>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H372" s="3"/>
+      <c r="I372" s="3"/>
+    </row>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H373" s="3"/>
+      <c r="I373" s="3"/>
+    </row>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H374" s="3"/>
+      <c r="I374" s="3"/>
+    </row>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H375" s="3"/>
+      <c r="I375" s="3"/>
+    </row>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H376" s="3"/>
+      <c r="I376" s="3"/>
+    </row>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H377" s="3"/>
+      <c r="I377" s="3"/>
+    </row>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H378" s="3"/>
+      <c r="I378" s="3"/>
+    </row>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H379" s="3"/>
+      <c r="I379" s="3"/>
+    </row>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H380" s="3"/>
+      <c r="I380" s="3"/>
+    </row>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H381" s="3"/>
+      <c r="I381" s="3"/>
+    </row>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H382" s="3"/>
+      <c r="I382" s="3"/>
+    </row>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H383" s="3"/>
+      <c r="I383" s="3"/>
+    </row>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H384" s="3"/>
+      <c r="I384" s="3"/>
+    </row>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H385" s="3"/>
+      <c r="I385" s="3"/>
+    </row>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H386" s="3"/>
+      <c r="I386" s="3"/>
+    </row>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H387" s="3"/>
+      <c r="I387" s="3"/>
+    </row>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H388" s="3"/>
+      <c r="I388" s="3"/>
+    </row>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H389" s="3"/>
+      <c r="I389" s="3"/>
+    </row>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H390" s="3"/>
+      <c r="I390" s="3"/>
+    </row>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H391" s="3"/>
+      <c r="I391" s="3"/>
+    </row>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H392" s="3"/>
+      <c r="I392" s="3"/>
+    </row>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H393" s="3"/>
+      <c r="I393" s="3"/>
+    </row>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H394" s="3"/>
+      <c r="I394" s="3"/>
+    </row>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H395" s="3"/>
+      <c r="I395" s="3"/>
+    </row>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H396" s="3"/>
+      <c r="I396" s="3"/>
+    </row>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H397" s="3"/>
+      <c r="I397" s="3"/>
+    </row>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H398" s="3"/>
+      <c r="I398" s="3"/>
+    </row>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H399" s="3"/>
+      <c r="I399" s="3"/>
+    </row>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H400" s="3"/>
+      <c r="I400" s="3"/>
+    </row>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H401" s="3"/>
+      <c r="I401" s="3"/>
+    </row>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H402" s="3"/>
+      <c r="I402" s="3"/>
+    </row>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H403" s="3"/>
+      <c r="I403" s="3"/>
+    </row>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H404" s="3"/>
+      <c r="I404" s="3"/>
+    </row>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H405" s="3"/>
+      <c r="I405" s="3"/>
+    </row>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H406" s="3"/>
+      <c r="I406" s="3"/>
+    </row>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H407" s="3"/>
+      <c r="I407" s="3"/>
+    </row>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H408" s="3"/>
+      <c r="I408" s="3"/>
+    </row>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H409" s="3"/>
+      <c r="I409" s="3"/>
+    </row>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H410" s="3"/>
+      <c r="I410" s="3"/>
+    </row>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H411" s="3"/>
+      <c r="I411" s="3"/>
+    </row>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H412" s="3"/>
+      <c r="I412" s="3"/>
+    </row>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H413" s="3"/>
+      <c r="I413" s="3"/>
+    </row>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H414" s="3"/>
+      <c r="I414" s="3"/>
+    </row>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H415" s="3"/>
+      <c r="I415" s="3"/>
+    </row>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H416" s="3"/>
+      <c r="I416" s="3"/>
+    </row>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H417" s="3"/>
+      <c r="I417" s="3"/>
+    </row>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H418" s="3"/>
+      <c r="I418" s="3"/>
+    </row>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H419" s="3"/>
+      <c r="I419" s="3"/>
+    </row>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H420" s="3"/>
+      <c r="I420" s="3"/>
+    </row>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H421" s="3"/>
+      <c r="I421" s="3"/>
+    </row>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H422" s="3"/>
+      <c r="I422" s="3"/>
+    </row>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H423" s="3"/>
+      <c r="I423" s="3"/>
+    </row>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H424" s="3"/>
+      <c r="I424" s="3"/>
+    </row>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H425" s="3"/>
+      <c r="I425" s="3"/>
+    </row>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H426" s="3"/>
+      <c r="I426" s="3"/>
+    </row>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H427" s="3"/>
+      <c r="I427" s="3"/>
+    </row>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H428" s="3"/>
+      <c r="I428" s="3"/>
+    </row>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H429" s="3"/>
+      <c r="I429" s="3"/>
+    </row>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H430" s="3"/>
+      <c r="I430" s="3"/>
+    </row>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H431" s="3"/>
+      <c r="I431" s="3"/>
+    </row>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H432" s="3"/>
+      <c r="I432" s="3"/>
+    </row>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H433" s="3"/>
+      <c r="I433" s="3"/>
+    </row>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H434" s="3"/>
+      <c r="I434" s="3"/>
+    </row>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H435" s="3"/>
+      <c r="I435" s="3"/>
+    </row>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H436" s="3"/>
+      <c r="I436" s="3"/>
+    </row>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H437" s="3"/>
+      <c r="I437" s="3"/>
+    </row>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H438" s="3"/>
+      <c r="I438" s="3"/>
+    </row>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H439" s="3"/>
+      <c r="I439" s="3"/>
+    </row>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H440" s="3"/>
+      <c r="I440" s="3"/>
+    </row>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H441" s="3"/>
+      <c r="I441" s="3"/>
+    </row>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H442" s="3"/>
+      <c r="I442" s="3"/>
+    </row>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H443" s="3"/>
+      <c r="I443" s="3"/>
+    </row>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H444" s="3"/>
+      <c r="I444" s="3"/>
+    </row>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H445" s="3"/>
+      <c r="I445" s="3"/>
+    </row>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H446" s="3"/>
+      <c r="I446" s="3"/>
+    </row>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H447" s="3"/>
+      <c r="I447" s="3"/>
+    </row>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H448" s="3"/>
+      <c r="I448" s="3"/>
+    </row>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H449" s="3"/>
+      <c r="I449" s="3"/>
+    </row>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H450" s="3"/>
+      <c r="I450" s="3"/>
+    </row>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H451" s="3"/>
+      <c r="I451" s="3"/>
+    </row>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H452" s="3"/>
+      <c r="I452" s="3"/>
+    </row>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H453" s="3"/>
+      <c r="I453" s="3"/>
+    </row>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H454" s="3"/>
+      <c r="I454" s="3"/>
+    </row>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H455" s="3"/>
+      <c r="I455" s="3"/>
+    </row>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H456" s="3"/>
+      <c r="I456" s="3"/>
+    </row>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H457" s="3"/>
+      <c r="I457" s="3"/>
+    </row>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H458" s="3"/>
+      <c r="I458" s="3"/>
+    </row>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H459" s="3"/>
+      <c r="I459" s="3"/>
+    </row>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H460" s="3"/>
+      <c r="I460" s="3"/>
+    </row>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H461" s="3"/>
+      <c r="I461" s="3"/>
+    </row>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H462" s="3"/>
+      <c r="I462" s="3"/>
+    </row>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H463" s="3"/>
+      <c r="I463" s="3"/>
+    </row>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H464" s="3"/>
+      <c r="I464" s="3"/>
+    </row>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H465" s="3"/>
+      <c r="I465" s="3"/>
+    </row>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H466" s="3"/>
+      <c r="I466" s="3"/>
+    </row>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H467" s="3"/>
+      <c r="I467" s="3"/>
+    </row>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H468" s="3"/>
+      <c r="I468" s="3"/>
+    </row>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H469" s="3"/>
+      <c r="I469" s="3"/>
+    </row>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H470" s="3"/>
+      <c r="I470" s="3"/>
+    </row>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H471" s="3"/>
+      <c r="I471" s="3"/>
+    </row>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H472" s="3"/>
+      <c r="I472" s="3"/>
+    </row>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H473" s="3"/>
+      <c r="I473" s="3"/>
+    </row>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H474" s="3"/>
+      <c r="I474" s="3"/>
+    </row>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H475" s="3"/>
+      <c r="I475" s="3"/>
+    </row>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H476" s="3"/>
+      <c r="I476" s="3"/>
+    </row>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H477" s="3"/>
+      <c r="I477" s="3"/>
+    </row>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H478" s="3"/>
+      <c r="I478" s="3"/>
+    </row>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H479" s="3"/>
+      <c r="I479" s="3"/>
+    </row>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H480" s="3"/>
+      <c r="I480" s="3"/>
+    </row>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H481" s="3"/>
+      <c r="I481" s="3"/>
+    </row>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H482" s="3"/>
+      <c r="I482" s="3"/>
+    </row>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H483" s="3"/>
+      <c r="I483" s="3"/>
+    </row>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H484" s="3"/>
+      <c r="I484" s="3"/>
+    </row>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H485" s="3"/>
+      <c r="I485" s="3"/>
+    </row>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H486" s="3"/>
+      <c r="I486" s="3"/>
+    </row>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H487" s="3"/>
+      <c r="I487" s="3"/>
+    </row>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H488" s="3"/>
+      <c r="I488" s="3"/>
+    </row>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H489" s="3"/>
+      <c r="I489" s="3"/>
+    </row>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H490" s="3"/>
+      <c r="I490" s="3"/>
+    </row>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H491" s="3"/>
+      <c r="I491" s="3"/>
+    </row>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H492" s="3"/>
+      <c r="I492" s="3"/>
+    </row>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H493" s="3"/>
+      <c r="I493" s="3"/>
+    </row>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H494" s="3"/>
+      <c r="I494" s="3"/>
+    </row>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H495" s="3"/>
+      <c r="I495" s="3"/>
+    </row>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H496" s="3"/>
+      <c r="I496" s="3"/>
+    </row>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H497" s="3"/>
+      <c r="I497" s="3"/>
+    </row>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H498" s="3"/>
+      <c r="I498" s="3"/>
+    </row>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H499" s="3"/>
+      <c r="I499" s="3"/>
+    </row>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H500" s="3"/>
+      <c r="I500" s="3"/>
+    </row>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H501" s="3"/>
+      <c r="I501" s="3"/>
+    </row>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H502" s="3"/>
+      <c r="I502" s="3"/>
+    </row>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H503" s="3"/>
+      <c r="I503" s="3"/>
+    </row>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H504" s="3"/>
+      <c r="I504" s="3"/>
+    </row>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H505" s="3"/>
+      <c r="I505" s="3"/>
+    </row>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H506" s="3"/>
+      <c r="I506" s="3"/>
+    </row>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H507" s="3"/>
+      <c r="I507" s="3"/>
+    </row>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H508" s="3"/>
+      <c r="I508" s="3"/>
+    </row>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H509" s="3"/>
+      <c r="I509" s="3"/>
+    </row>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H510" s="3"/>
+      <c r="I510" s="3"/>
+    </row>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H511" s="3"/>
+      <c r="I511" s="3"/>
+    </row>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H512" s="3"/>
+      <c r="I512" s="3"/>
+    </row>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H513" s="3"/>
+      <c r="I513" s="3"/>
+    </row>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H514" s="3"/>
+      <c r="I514" s="3"/>
+    </row>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H515" s="3"/>
+      <c r="I515" s="3"/>
+    </row>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H516" s="3"/>
+      <c r="I516" s="3"/>
+    </row>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H517" s="3"/>
+      <c r="I517" s="3"/>
+    </row>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H518" s="3"/>
+      <c r="I518" s="3"/>
+    </row>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H519" s="3"/>
+      <c r="I519" s="3"/>
+    </row>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H520" s="3"/>
+      <c r="I520" s="3"/>
+    </row>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H521" s="3"/>
+      <c r="I521" s="3"/>
+    </row>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H522" s="3"/>
+      <c r="I522" s="3"/>
+    </row>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H523" s="3"/>
+      <c r="I523" s="3"/>
+    </row>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H524" s="3"/>
+      <c r="I524" s="3"/>
+    </row>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H525" s="3"/>
+      <c r="I525" s="3"/>
+    </row>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H526" s="3"/>
+      <c r="I526" s="3"/>
+    </row>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H527" s="3"/>
+      <c r="I527" s="3"/>
+    </row>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H528" s="3"/>
+      <c r="I528" s="3"/>
+    </row>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H529" s="3"/>
+      <c r="I529" s="3"/>
+    </row>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H530" s="3"/>
+      <c r="I530" s="3"/>
+    </row>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H531" s="3"/>
+      <c r="I531" s="3"/>
+    </row>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H532" s="3"/>
+      <c r="I532" s="3"/>
+    </row>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H533" s="3"/>
+      <c r="I533" s="3"/>
+    </row>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H534" s="3"/>
+      <c r="I534" s="3"/>
+    </row>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H535" s="3"/>
+      <c r="I535" s="3"/>
+    </row>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H536" s="3"/>
+      <c r="I536" s="3"/>
+    </row>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H537" s="3"/>
+      <c r="I537" s="3"/>
+    </row>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H538" s="3"/>
+      <c r="I538" s="3"/>
+    </row>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H539" s="3"/>
+      <c r="I539" s="3"/>
+    </row>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H540" s="3"/>
+      <c r="I540" s="3"/>
+    </row>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H541" s="3"/>
+      <c r="I541" s="3"/>
+    </row>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H542" s="3"/>
+      <c r="I542" s="3"/>
+    </row>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H543" s="3"/>
+      <c r="I543" s="3"/>
+    </row>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H544" s="3"/>
+      <c r="I544" s="3"/>
+    </row>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H545" s="3"/>
+      <c r="I545" s="3"/>
+    </row>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H546" s="3"/>
+      <c r="I546" s="3"/>
+    </row>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H547" s="3"/>
+      <c r="I547" s="3"/>
+    </row>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H548" s="3"/>
+      <c r="I548" s="3"/>
+    </row>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H549" s="3"/>
+      <c r="I549" s="3"/>
+    </row>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H550" s="3"/>
+      <c r="I550" s="3"/>
+    </row>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H551" s="3"/>
+      <c r="I551" s="3"/>
+    </row>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H552" s="3"/>
+      <c r="I552" s="3"/>
+    </row>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H553" s="3"/>
+      <c r="I553" s="3"/>
+    </row>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H554" s="3"/>
+      <c r="I554" s="3"/>
+    </row>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H555" s="3"/>
+      <c r="I555" s="3"/>
+    </row>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H556" s="3"/>
+      <c r="I556" s="3"/>
+    </row>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H557" s="3"/>
+      <c r="I557" s="3"/>
+    </row>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H558" s="3"/>
+      <c r="I558" s="3"/>
+    </row>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H559" s="3"/>
+      <c r="I559" s="3"/>
+    </row>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H560" s="3"/>
+      <c r="I560" s="3"/>
+    </row>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H561" s="3"/>
+      <c r="I561" s="3"/>
+    </row>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H562" s="3"/>
+      <c r="I562" s="3"/>
+    </row>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H563" s="3"/>
+      <c r="I563" s="3"/>
+    </row>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H564" s="3"/>
+      <c r="I564" s="3"/>
+    </row>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H565" s="3"/>
+      <c r="I565" s="3"/>
+    </row>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H566" s="3"/>
+      <c r="I566" s="3"/>
+    </row>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H567" s="3"/>
+      <c r="I567" s="3"/>
+    </row>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H568" s="3"/>
+      <c r="I568" s="3"/>
+    </row>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H569" s="3"/>
+      <c r="I569" s="3"/>
+    </row>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H570" s="3"/>
+      <c r="I570" s="3"/>
+    </row>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H571" s="3"/>
+      <c r="I571" s="3"/>
+    </row>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H572" s="3"/>
+      <c r="I572" s="3"/>
+    </row>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H573" s="3"/>
+      <c r="I573" s="3"/>
+    </row>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H574" s="3"/>
+      <c r="I574" s="3"/>
+    </row>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H575" s="3"/>
+      <c r="I575" s="3"/>
+    </row>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H576" s="3"/>
+      <c r="I576" s="3"/>
+    </row>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H577" s="3"/>
+      <c r="I577" s="3"/>
+    </row>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H578" s="3"/>
+      <c r="I578" s="3"/>
+    </row>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H579" s="3"/>
+      <c r="I579" s="3"/>
+    </row>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H580" s="3"/>
+      <c r="I580" s="3"/>
+    </row>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H581" s="3"/>
+      <c r="I581" s="3"/>
+    </row>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H582" s="3"/>
+      <c r="I582" s="3"/>
+    </row>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H583" s="3"/>
+      <c r="I583" s="3"/>
+    </row>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H584" s="3"/>
+      <c r="I584" s="3"/>
+    </row>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H585" s="3"/>
+      <c r="I585" s="3"/>
+    </row>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H586" s="3"/>
+      <c r="I586" s="3"/>
+    </row>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H587" s="3"/>
+      <c r="I587" s="3"/>
+    </row>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H588" s="3"/>
+      <c r="I588" s="3"/>
+    </row>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H589" s="3"/>
+      <c r="I589" s="3"/>
+    </row>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H590" s="3"/>
+      <c r="I590" s="3"/>
+    </row>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H591" s="3"/>
+      <c r="I591" s="3"/>
+    </row>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H592" s="3"/>
+      <c r="I592" s="3"/>
+    </row>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H593" s="3"/>
+      <c r="I593" s="3"/>
+    </row>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H594" s="3"/>
+      <c r="I594" s="3"/>
+    </row>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H595" s="3"/>
+      <c r="I595" s="3"/>
+    </row>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H596" s="3"/>
+      <c r="I596" s="3"/>
+    </row>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H597" s="3"/>
+      <c r="I597" s="3"/>
+    </row>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H598" s="3"/>
+      <c r="I598" s="3"/>
+    </row>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H599" s="3"/>
+      <c r="I599" s="3"/>
+    </row>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H600" s="3"/>
+      <c r="I600" s="3"/>
+    </row>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H601" s="3"/>
+      <c r="I601" s="3"/>
+    </row>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H602" s="3"/>
+      <c r="I602" s="3"/>
+    </row>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H603" s="3"/>
+      <c r="I603" s="3"/>
+    </row>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H604" s="3"/>
+      <c r="I604" s="3"/>
+    </row>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H605" s="3"/>
+      <c r="I605" s="3"/>
+    </row>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H606" s="3"/>
+      <c r="I606" s="3"/>
+    </row>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H607" s="3"/>
+      <c r="I607" s="3"/>
+    </row>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H608" s="3"/>
+      <c r="I608" s="3"/>
+    </row>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H609" s="3"/>
+      <c r="I609" s="3"/>
+    </row>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H610" s="3"/>
+      <c r="I610" s="3"/>
+    </row>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H611" s="3"/>
+      <c r="I611" s="3"/>
+    </row>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H612" s="3"/>
+      <c r="I612" s="3"/>
+    </row>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H613" s="3"/>
+      <c r="I613" s="3"/>
+    </row>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H614" s="3"/>
+      <c r="I614" s="3"/>
+    </row>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H615" s="3"/>
+      <c r="I615" s="3"/>
+    </row>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H616" s="3"/>
+      <c r="I616" s="3"/>
+    </row>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H617" s="3"/>
+      <c r="I617" s="3"/>
+    </row>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H618" s="3"/>
+      <c r="I618" s="3"/>
+    </row>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H619" s="3"/>
+      <c r="I619" s="3"/>
+    </row>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H620" s="3"/>
+      <c r="I620" s="3"/>
+    </row>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H621" s="3"/>
+      <c r="I621" s="3"/>
+    </row>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H622" s="3"/>
+      <c r="I622" s="3"/>
+    </row>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H623" s="3"/>
+      <c r="I623" s="3"/>
+    </row>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H624" s="3"/>
+      <c r="I624" s="3"/>
+    </row>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H625" s="3"/>
+      <c r="I625" s="3"/>
+    </row>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H626" s="3"/>
+      <c r="I626" s="3"/>
+    </row>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H627" s="3"/>
+      <c r="I627" s="3"/>
+    </row>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H628" s="3"/>
+      <c r="I628" s="3"/>
+    </row>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H629" s="3"/>
+      <c r="I629" s="3"/>
+    </row>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H630" s="3"/>
+      <c r="I630" s="3"/>
+    </row>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H631" s="3"/>
+      <c r="I631" s="3"/>
+    </row>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H632" s="3"/>
+      <c r="I632" s="3"/>
+    </row>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H633" s="3"/>
+      <c r="I633" s="3"/>
+    </row>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H634" s="3"/>
+      <c r="I634" s="3"/>
+    </row>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H635" s="3"/>
+      <c r="I635" s="3"/>
+    </row>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H636" s="3"/>
+      <c r="I636" s="3"/>
+    </row>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H637" s="3"/>
+      <c r="I637" s="3"/>
+    </row>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H638" s="3"/>
+      <c r="I638" s="3"/>
+    </row>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H639" s="3"/>
+      <c r="I639" s="3"/>
+    </row>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H640" s="3"/>
+      <c r="I640" s="3"/>
+    </row>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H641" s="3"/>
+      <c r="I641" s="3"/>
+    </row>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H642" s="3"/>
+      <c r="I642" s="3"/>
+    </row>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H643" s="3"/>
+      <c r="I643" s="3"/>
+    </row>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H644" s="3"/>
+      <c r="I644" s="3"/>
+    </row>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H645" s="3"/>
+      <c r="I645" s="3"/>
+    </row>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H646" s="3"/>
+      <c r="I646" s="3"/>
+    </row>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H647" s="3"/>
+      <c r="I647" s="3"/>
+    </row>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H648" s="3"/>
+      <c r="I648" s="3"/>
+    </row>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H649" s="3"/>
+      <c r="I649" s="3"/>
+    </row>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H650" s="3"/>
+      <c r="I650" s="3"/>
+    </row>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H651" s="3"/>
+      <c r="I651" s="3"/>
+    </row>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H652" s="3"/>
+      <c r="I652" s="3"/>
+    </row>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H653" s="3"/>
+      <c r="I653" s="3"/>
+    </row>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H654" s="3"/>
+      <c r="I654" s="3"/>
+    </row>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H655" s="3"/>
+      <c r="I655" s="3"/>
+    </row>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H656" s="3"/>
+      <c r="I656" s="3"/>
+    </row>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H657" s="3"/>
+      <c r="I657" s="3"/>
+    </row>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H658" s="3"/>
+      <c r="I658" s="3"/>
+    </row>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H659" s="3"/>
+      <c r="I659" s="3"/>
+    </row>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H660" s="3"/>
+      <c r="I660" s="3"/>
+    </row>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H661" s="3"/>
+      <c r="I661" s="3"/>
+    </row>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H662" s="3"/>
+      <c r="I662" s="3"/>
+    </row>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H663" s="3"/>
+      <c r="I663" s="3"/>
+    </row>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H664" s="3"/>
+      <c r="I664" s="3"/>
+    </row>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H665" s="3"/>
+      <c r="I665" s="3"/>
+    </row>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H666" s="3"/>
+      <c r="I666" s="3"/>
+    </row>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H667" s="3"/>
+      <c r="I667" s="3"/>
+    </row>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H668" s="3"/>
+      <c r="I668" s="3"/>
+    </row>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H669" s="3"/>
+      <c r="I669" s="3"/>
+    </row>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H670" s="3"/>
+      <c r="I670" s="3"/>
+    </row>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H671" s="3"/>
+      <c r="I671" s="3"/>
+    </row>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H672" s="3"/>
+      <c r="I672" s="3"/>
+    </row>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H673" s="3"/>
+      <c r="I673" s="3"/>
+    </row>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H674" s="3"/>
+      <c r="I674" s="3"/>
+    </row>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H675" s="3"/>
+      <c r="I675" s="3"/>
+    </row>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H676" s="3"/>
+      <c r="I676" s="3"/>
+    </row>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H677" s="3"/>
+      <c r="I677" s="3"/>
+    </row>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H678" s="3"/>
+      <c r="I678" s="3"/>
+    </row>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H679" s="3"/>
+      <c r="I679" s="3"/>
+    </row>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H680" s="3"/>
+      <c r="I680" s="3"/>
+    </row>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H681" s="3"/>
+      <c r="I681" s="3"/>
+    </row>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H682" s="3"/>
+      <c r="I682" s="3"/>
+    </row>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H683" s="3"/>
+      <c r="I683" s="3"/>
+    </row>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H684" s="3"/>
+      <c r="I684" s="3"/>
+    </row>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H685" s="3"/>
+      <c r="I685" s="3"/>
+    </row>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H686" s="3"/>
+      <c r="I686" s="3"/>
+    </row>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H687" s="3"/>
+      <c r="I687" s="3"/>
+    </row>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H688" s="3"/>
+      <c r="I688" s="3"/>
+    </row>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H689" s="3"/>
+      <c r="I689" s="3"/>
+    </row>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H690" s="3"/>
+      <c r="I690" s="3"/>
+    </row>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H691" s="3"/>
+      <c r="I691" s="3"/>
+    </row>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H692" s="3"/>
+      <c r="I692" s="3"/>
+    </row>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H693" s="3"/>
+      <c r="I693" s="3"/>
+    </row>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H694" s="3"/>
+      <c r="I694" s="3"/>
+    </row>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H695" s="3"/>
+      <c r="I695" s="3"/>
+    </row>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H696" s="3"/>
+      <c r="I696" s="3"/>
+    </row>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H697" s="3"/>
+      <c r="I697" s="3"/>
+    </row>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H698" s="3"/>
+      <c r="I698" s="3"/>
+    </row>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H699" s="3"/>
+      <c r="I699" s="3"/>
+    </row>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H700" s="3"/>
+      <c r="I700" s="3"/>
+    </row>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H701" s="3"/>
+      <c r="I701" s="3"/>
+    </row>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H702" s="3"/>
+      <c r="I702" s="3"/>
+    </row>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H703" s="3"/>
+      <c r="I703" s="3"/>
+    </row>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H704" s="3"/>
+      <c r="I704" s="3"/>
+    </row>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H705" s="3"/>
+      <c r="I705" s="3"/>
+    </row>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H706" s="3"/>
+      <c r="I706" s="3"/>
+    </row>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H707" s="3"/>
+      <c r="I707" s="3"/>
+    </row>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H708" s="3"/>
+      <c r="I708" s="3"/>
+    </row>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H709" s="3"/>
+      <c r="I709" s="3"/>
+    </row>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H710" s="3"/>
+      <c r="I710" s="3"/>
+    </row>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H711" s="3"/>
+      <c r="I711" s="3"/>
+    </row>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H712" s="3"/>
+      <c r="I712" s="3"/>
+    </row>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H713" s="3"/>
+      <c r="I713" s="3"/>
+    </row>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H714" s="3"/>
+      <c r="I714" s="3"/>
+    </row>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H715" s="3"/>
+      <c r="I715" s="3"/>
+    </row>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H716" s="3"/>
+      <c r="I716" s="3"/>
+    </row>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H717" s="3"/>
+      <c r="I717" s="3"/>
+    </row>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H718" s="3"/>
+      <c r="I718" s="3"/>
+    </row>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H719" s="3"/>
+      <c r="I719" s="3"/>
+    </row>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H720" s="3"/>
+      <c r="I720" s="3"/>
+    </row>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H721" s="3"/>
+      <c r="I721" s="3"/>
+    </row>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H722" s="3"/>
+      <c r="I722" s="3"/>
+    </row>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H723" s="3"/>
+      <c r="I723" s="3"/>
+    </row>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H724" s="3"/>
+      <c r="I724" s="3"/>
+    </row>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H725" s="3"/>
+      <c r="I725" s="3"/>
+    </row>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H726" s="3"/>
+      <c r="I726" s="3"/>
+    </row>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H727" s="3"/>
+      <c r="I727" s="3"/>
+    </row>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H728" s="3"/>
+      <c r="I728" s="3"/>
+    </row>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H729" s="3"/>
+      <c r="I729" s="3"/>
+    </row>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H730" s="3"/>
+      <c r="I730" s="3"/>
+    </row>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H731" s="3"/>
+      <c r="I731" s="3"/>
+    </row>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H732" s="3"/>
+      <c r="I732" s="3"/>
+    </row>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H733" s="3"/>
+      <c r="I733" s="3"/>
+    </row>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H734" s="3"/>
+      <c r="I734" s="3"/>
+    </row>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H735" s="3"/>
+      <c r="I735" s="3"/>
+    </row>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H736" s="3"/>
+      <c r="I736" s="3"/>
+    </row>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H737" s="3"/>
+      <c r="I737" s="3"/>
+    </row>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H738" s="3"/>
+      <c r="I738" s="3"/>
+    </row>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H739" s="3"/>
+      <c r="I739" s="3"/>
+    </row>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H740" s="3"/>
+      <c r="I740" s="3"/>
+    </row>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H741" s="3"/>
+      <c r="I741" s="3"/>
+    </row>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H742" s="3"/>
+      <c r="I742" s="3"/>
+    </row>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H743" s="3"/>
+      <c r="I743" s="3"/>
+    </row>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H744" s="3"/>
+      <c r="I744" s="3"/>
+    </row>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H745" s="3"/>
+      <c r="I745" s="3"/>
+    </row>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H746" s="3"/>
+      <c r="I746" s="3"/>
+    </row>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H747" s="3"/>
+      <c r="I747" s="3"/>
+    </row>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H748" s="3"/>
+      <c r="I748" s="3"/>
+    </row>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H749" s="3"/>
+      <c r="I749" s="3"/>
+    </row>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H750" s="3"/>
+      <c r="I750" s="3"/>
+    </row>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H751" s="3"/>
+      <c r="I751" s="3"/>
+    </row>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H752" s="3"/>
+      <c r="I752" s="3"/>
+    </row>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H753" s="3"/>
+      <c r="I753" s="3"/>
+    </row>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H754" s="3"/>
+      <c r="I754" s="3"/>
+    </row>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H755" s="3"/>
+      <c r="I755" s="3"/>
+    </row>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H756" s="3"/>
+      <c r="I756" s="3"/>
+    </row>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H757" s="3"/>
+      <c r="I757" s="3"/>
+    </row>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H758" s="3"/>
+      <c r="I758" s="3"/>
+    </row>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H759" s="3"/>
+      <c r="I759" s="3"/>
+    </row>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H760" s="3"/>
+      <c r="I760" s="3"/>
+    </row>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H761" s="3"/>
+      <c r="I761" s="3"/>
+    </row>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H762" s="3"/>
+      <c r="I762" s="3"/>
+    </row>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H763" s="3"/>
+      <c r="I763" s="3"/>
+    </row>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H764" s="3"/>
+      <c r="I764" s="3"/>
+    </row>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H765" s="3"/>
+      <c r="I765" s="3"/>
+    </row>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H766" s="3"/>
+      <c r="I766" s="3"/>
+    </row>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H767" s="3"/>
+      <c r="I767" s="3"/>
+    </row>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H768" s="3"/>
+      <c r="I768" s="3"/>
+    </row>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H769" s="3"/>
+      <c r="I769" s="3"/>
+    </row>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H770" s="3"/>
+      <c r="I770" s="3"/>
+    </row>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H771" s="3"/>
+      <c r="I771" s="3"/>
+    </row>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H772" s="3"/>
+      <c r="I772" s="3"/>
+    </row>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H773" s="3"/>
+      <c r="I773" s="3"/>
+    </row>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H774" s="3"/>
+      <c r="I774" s="3"/>
+    </row>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H775" s="3"/>
+      <c r="I775" s="3"/>
+    </row>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H776" s="3"/>
+      <c r="I776" s="3"/>
+    </row>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H777" s="3"/>
+      <c r="I777" s="3"/>
+    </row>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H778" s="3"/>
+      <c r="I778" s="3"/>
+    </row>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H779" s="3"/>
+      <c r="I779" s="3"/>
+    </row>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H780" s="3"/>
+      <c r="I780" s="3"/>
+    </row>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H781" s="3"/>
+      <c r="I781" s="3"/>
+    </row>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H782" s="3"/>
+      <c r="I782" s="3"/>
+    </row>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H783" s="3"/>
+      <c r="I783" s="3"/>
+    </row>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H784" s="3"/>
+      <c r="I784" s="3"/>
+    </row>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H785" s="3"/>
+      <c r="I785" s="3"/>
+    </row>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H786" s="3"/>
+      <c r="I786" s="3"/>
+    </row>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H787" s="3"/>
+      <c r="I787" s="3"/>
+    </row>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H788" s="3"/>
+      <c r="I788" s="3"/>
+    </row>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H789" s="3"/>
+      <c r="I789" s="3"/>
+    </row>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H790" s="3"/>
+      <c r="I790" s="3"/>
+    </row>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H791" s="3"/>
+      <c r="I791" s="3"/>
+    </row>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H792" s="3"/>
+      <c r="I792" s="3"/>
+    </row>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H793" s="3"/>
+      <c r="I793" s="3"/>
+    </row>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H794" s="3"/>
+      <c r="I794" s="3"/>
+    </row>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H795" s="3"/>
+      <c r="I795" s="3"/>
+    </row>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H796" s="3"/>
+      <c r="I796" s="3"/>
+    </row>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H797" s="3"/>
+      <c r="I797" s="3"/>
+    </row>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H798" s="3"/>
+      <c r="I798" s="3"/>
+    </row>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H799" s="3"/>
+      <c r="I799" s="3"/>
+    </row>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H800" s="3"/>
+      <c r="I800" s="3"/>
+    </row>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H801" s="3"/>
+      <c r="I801" s="3"/>
+    </row>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H802" s="3"/>
+      <c r="I802" s="3"/>
+    </row>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H803" s="3"/>
+      <c r="I803" s="3"/>
+    </row>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H804" s="3"/>
+      <c r="I804" s="3"/>
+    </row>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H805" s="3"/>
+      <c r="I805" s="3"/>
+    </row>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H806" s="3"/>
+      <c r="I806" s="3"/>
+    </row>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H807" s="3"/>
+      <c r="I807" s="3"/>
+    </row>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H808" s="3"/>
+      <c r="I808" s="3"/>
+    </row>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H809" s="3"/>
+      <c r="I809" s="3"/>
+    </row>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H810" s="3"/>
+      <c r="I810" s="3"/>
+    </row>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H811" s="3"/>
+      <c r="I811" s="3"/>
+    </row>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H812" s="3"/>
+      <c r="I812" s="3"/>
+    </row>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H813" s="3"/>
+      <c r="I813" s="3"/>
+    </row>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H814" s="3"/>
+      <c r="I814" s="3"/>
+    </row>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H815" s="3"/>
+      <c r="I815" s="3"/>
+    </row>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H816" s="3"/>
+      <c r="I816" s="3"/>
+    </row>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H817" s="3"/>
+      <c r="I817" s="3"/>
+    </row>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H818" s="3"/>
+      <c r="I818" s="3"/>
+    </row>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H819" s="3"/>
+      <c r="I819" s="3"/>
+    </row>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H820" s="3"/>
+      <c r="I820" s="3"/>
+    </row>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H821" s="3"/>
+      <c r="I821" s="3"/>
+    </row>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H822" s="3"/>
+      <c r="I822" s="3"/>
+    </row>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H823" s="3"/>
+      <c r="I823" s="3"/>
+    </row>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H824" s="3"/>
+      <c r="I824" s="3"/>
+    </row>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H825" s="3"/>
+      <c r="I825" s="3"/>
+    </row>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H826" s="3"/>
+      <c r="I826" s="3"/>
+    </row>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H827" s="3"/>
+      <c r="I827" s="3"/>
+    </row>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H828" s="3"/>
+      <c r="I828" s="3"/>
+    </row>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H829" s="3"/>
+      <c r="I829" s="3"/>
+    </row>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H830" s="3"/>
+      <c r="I830" s="3"/>
+    </row>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H831" s="3"/>
+      <c r="I831" s="3"/>
+    </row>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H832" s="3"/>
+      <c r="I832" s="3"/>
+    </row>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H833" s="3"/>
+      <c r="I833" s="3"/>
+    </row>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H834" s="3"/>
+      <c r="I834" s="3"/>
+    </row>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H835" s="3"/>
+      <c r="I835" s="3"/>
+    </row>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H836" s="3"/>
+      <c r="I836" s="3"/>
+    </row>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H837" s="3"/>
+      <c r="I837" s="3"/>
+    </row>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H838" s="3"/>
+      <c r="I838" s="3"/>
+    </row>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H839" s="3"/>
+      <c r="I839" s="3"/>
+    </row>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H840" s="3"/>
+      <c r="I840" s="3"/>
+    </row>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H841" s="3"/>
+      <c r="I841" s="3"/>
+    </row>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H842" s="3"/>
+      <c r="I842" s="3"/>
+    </row>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H843" s="3"/>
+      <c r="I843" s="3"/>
+    </row>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H844" s="3"/>
+      <c r="I844" s="3"/>
+    </row>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H845" s="3"/>
+      <c r="I845" s="3"/>
+    </row>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H846" s="3"/>
+      <c r="I846" s="3"/>
+    </row>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H847" s="3"/>
+      <c r="I847" s="3"/>
+    </row>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H848" s="3"/>
+      <c r="I848" s="3"/>
+    </row>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H849" s="3"/>
+      <c r="I849" s="3"/>
+    </row>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H850" s="3"/>
+      <c r="I850" s="3"/>
+    </row>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H851" s="3"/>
+      <c r="I851" s="3"/>
+    </row>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H852" s="3"/>
+      <c r="I852" s="3"/>
+    </row>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H853" s="3"/>
+      <c r="I853" s="3"/>
+    </row>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H854" s="3"/>
+      <c r="I854" s="3"/>
+    </row>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H855" s="3"/>
+      <c r="I855" s="3"/>
+    </row>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H856" s="3"/>
+      <c r="I856" s="3"/>
+    </row>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H857" s="3"/>
+      <c r="I857" s="3"/>
+    </row>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H858" s="3"/>
+      <c r="I858" s="3"/>
+    </row>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H859" s="3"/>
+      <c r="I859" s="3"/>
+    </row>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H860" s="3"/>
+      <c r="I860" s="3"/>
+    </row>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H861" s="3"/>
+      <c r="I861" s="3"/>
+    </row>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H862" s="3"/>
+      <c r="I862" s="3"/>
+    </row>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H863" s="3"/>
+      <c r="I863" s="3"/>
+    </row>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H864" s="3"/>
+      <c r="I864" s="3"/>
+    </row>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H865" s="3"/>
+      <c r="I865" s="3"/>
+    </row>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H866" s="3"/>
+      <c r="I866" s="3"/>
+    </row>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H867" s="3"/>
+      <c r="I867" s="3"/>
+    </row>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H868" s="3"/>
+      <c r="I868" s="3"/>
+    </row>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H869" s="3"/>
+      <c r="I869" s="3"/>
+    </row>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H870" s="3"/>
+      <c r="I870" s="3"/>
+    </row>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H871" s="3"/>
+      <c r="I871" s="3"/>
+    </row>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H872" s="3"/>
+      <c r="I872" s="3"/>
+    </row>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H873" s="3"/>
+      <c r="I873" s="3"/>
+    </row>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H874" s="3"/>
+      <c r="I874" s="3"/>
+    </row>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H875" s="3"/>
+      <c r="I875" s="3"/>
+    </row>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H876" s="3"/>
+      <c r="I876" s="3"/>
+    </row>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H877" s="3"/>
+      <c r="I877" s="3"/>
+    </row>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H878" s="3"/>
+      <c r="I878" s="3"/>
+    </row>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H879" s="3"/>
+      <c r="I879" s="3"/>
+    </row>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H880" s="3"/>
+      <c r="I880" s="3"/>
+    </row>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H881" s="3"/>
+      <c r="I881" s="3"/>
+    </row>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H882" s="3"/>
+      <c r="I882" s="3"/>
+    </row>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H883" s="3"/>
+      <c r="I883" s="3"/>
+    </row>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H884" s="3"/>
+      <c r="I884" s="3"/>
+    </row>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H885" s="3"/>
+      <c r="I885" s="3"/>
+    </row>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H886" s="3"/>
+      <c r="I886" s="3"/>
+    </row>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H887" s="3"/>
+      <c r="I887" s="3"/>
+    </row>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H888" s="3"/>
+      <c r="I888" s="3"/>
+    </row>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H889" s="3"/>
+      <c r="I889" s="3"/>
+    </row>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H890" s="3"/>
+      <c r="I890" s="3"/>
+    </row>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H891" s="3"/>
+      <c r="I891" s="3"/>
+    </row>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H892" s="3"/>
+      <c r="I892" s="3"/>
+    </row>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H893" s="3"/>
+      <c r="I893" s="3"/>
+    </row>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H894" s="3"/>
+      <c r="I894" s="3"/>
+    </row>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H895" s="3"/>
+      <c r="I895" s="3"/>
+    </row>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H896" s="3"/>
+      <c r="I896" s="3"/>
+    </row>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H897" s="3"/>
+      <c r="I897" s="3"/>
+    </row>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H898" s="3"/>
+      <c r="I898" s="3"/>
+    </row>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H899" s="3"/>
+      <c r="I899" s="3"/>
+    </row>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H900" s="3"/>
+      <c r="I900" s="3"/>
+    </row>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H901" s="3"/>
+      <c r="I901" s="3"/>
+    </row>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H902" s="3"/>
+      <c r="I902" s="3"/>
+    </row>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H903" s="3"/>
+      <c r="I903" s="3"/>
+    </row>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H904" s="3"/>
+      <c r="I904" s="3"/>
+    </row>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H905" s="3"/>
+      <c r="I905" s="3"/>
+    </row>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H906" s="3"/>
+      <c r="I906" s="3"/>
+    </row>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H907" s="3"/>
+      <c r="I907" s="3"/>
+    </row>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H908" s="3"/>
+      <c r="I908" s="3"/>
+    </row>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H909" s="3"/>
+      <c r="I909" s="3"/>
+    </row>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H910" s="3"/>
+      <c r="I910" s="3"/>
+    </row>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H911" s="3"/>
+      <c r="I911" s="3"/>
+    </row>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H912" s="3"/>
+      <c r="I912" s="3"/>
+    </row>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H913" s="3"/>
+      <c r="I913" s="3"/>
+    </row>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H914" s="3"/>
+      <c r="I914" s="3"/>
+    </row>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H915" s="3"/>
+      <c r="I915" s="3"/>
+    </row>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H916" s="3"/>
+      <c r="I916" s="3"/>
+    </row>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H917" s="3"/>
+      <c r="I917" s="3"/>
+    </row>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H918" s="3"/>
+      <c r="I918" s="3"/>
+    </row>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H919" s="3"/>
+      <c r="I919" s="3"/>
+    </row>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H920" s="3"/>
+      <c r="I920" s="3"/>
+    </row>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H921" s="3"/>
+      <c r="I921" s="3"/>
+    </row>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H922" s="3"/>
+      <c r="I922" s="3"/>
+    </row>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H923" s="3"/>
+      <c r="I923" s="3"/>
+    </row>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H924" s="3"/>
+      <c r="I924" s="3"/>
+    </row>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H925" s="3"/>
+      <c r="I925" s="3"/>
+    </row>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H926" s="3"/>
+      <c r="I926" s="3"/>
+    </row>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H927" s="3"/>
+      <c r="I927" s="3"/>
+    </row>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H928" s="3"/>
+      <c r="I928" s="3"/>
+    </row>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H929" s="3"/>
+      <c r="I929" s="3"/>
+    </row>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H930" s="3"/>
+      <c r="I930" s="3"/>
+    </row>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H931" s="3"/>
+      <c r="I931" s="3"/>
+    </row>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H932" s="3"/>
+      <c r="I932" s="3"/>
+    </row>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H933" s="3"/>
+      <c r="I933" s="3"/>
+    </row>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H934" s="3"/>
+      <c r="I934" s="3"/>
+    </row>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H935" s="3"/>
+      <c r="I935" s="3"/>
+    </row>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H936" s="3"/>
+      <c r="I936" s="3"/>
+    </row>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H937" s="3"/>
+      <c r="I937" s="3"/>
+    </row>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H938" s="3"/>
+      <c r="I938" s="3"/>
+    </row>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H939" s="3"/>
+      <c r="I939" s="3"/>
+    </row>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H940" s="3"/>
+      <c r="I940" s="3"/>
+    </row>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H941" s="3"/>
+      <c r="I941" s="3"/>
+    </row>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H942" s="3"/>
+      <c r="I942" s="3"/>
+    </row>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H943" s="3"/>
+      <c r="I943" s="3"/>
+    </row>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H944" s="3"/>
+      <c r="I944" s="3"/>
+    </row>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H945" s="3"/>
+      <c r="I945" s="3"/>
+    </row>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H946" s="3"/>
+      <c r="I946" s="3"/>
+    </row>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H947" s="3"/>
+      <c r="I947" s="3"/>
+    </row>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H948" s="3"/>
+      <c r="I948" s="3"/>
+    </row>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H949" s="3"/>
+      <c r="I949" s="3"/>
+    </row>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H950" s="3"/>
+      <c r="I950" s="3"/>
+    </row>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H951" s="3"/>
+      <c r="I951" s="3"/>
+    </row>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H952" s="3"/>
+      <c r="I952" s="3"/>
+    </row>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H953" s="3"/>
+      <c r="I953" s="3"/>
+    </row>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H954" s="3"/>
+      <c r="I954" s="3"/>
+    </row>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H955" s="3"/>
+      <c r="I955" s="3"/>
+    </row>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H956" s="3"/>
+      <c r="I956" s="3"/>
+    </row>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H957" s="3"/>
+      <c r="I957" s="3"/>
+    </row>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H958" s="3"/>
+      <c r="I958" s="3"/>
+    </row>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H959" s="3"/>
+      <c r="I959" s="3"/>
+    </row>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H960" s="3"/>
+      <c r="I960" s="3"/>
+    </row>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H961" s="3"/>
+      <c r="I961" s="3"/>
+    </row>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H962" s="3"/>
+      <c r="I962" s="3"/>
+    </row>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H963" s="3"/>
+      <c r="I963" s="3"/>
+    </row>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H964" s="3"/>
+      <c r="I964" s="3"/>
+    </row>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H965" s="3"/>
+      <c r="I965" s="3"/>
+    </row>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H966" s="3"/>
+      <c r="I966" s="3"/>
+    </row>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H967" s="3"/>
+      <c r="I967" s="3"/>
+    </row>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H968" s="3"/>
+      <c r="I968" s="3"/>
+    </row>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H969" s="3"/>
+      <c r="I969" s="3"/>
+    </row>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H970" s="3"/>
+      <c r="I970" s="3"/>
+    </row>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H971" s="3"/>
+      <c r="I971" s="3"/>
+    </row>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H972" s="3"/>
+      <c r="I972" s="3"/>
+    </row>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H973" s="3"/>
+      <c r="I973" s="3"/>
+    </row>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H974" s="3"/>
+      <c r="I974" s="3"/>
+    </row>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H975" s="3"/>
+      <c r="I975" s="3"/>
+    </row>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H976" s="3"/>
+      <c r="I976" s="3"/>
+    </row>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H977" s="3"/>
+      <c r="I977" s="3"/>
+    </row>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H978" s="3"/>
+      <c r="I978" s="3"/>
+    </row>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H979" s="3"/>
+      <c r="I979" s="3"/>
+    </row>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H980" s="3"/>
+      <c r="I980" s="3"/>
+    </row>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H981" s="3"/>
+      <c r="I981" s="3"/>
+    </row>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H982" s="3"/>
+      <c r="I982" s="3"/>
+    </row>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H983" s="3"/>
+      <c r="I983" s="3"/>
+    </row>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H984" s="3"/>
+      <c r="I984" s="3"/>
+    </row>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H985" s="3"/>
+      <c r="I985" s="3"/>
+    </row>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H986" s="3"/>
+      <c r="I986" s="3"/>
+    </row>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H987" s="3"/>
+      <c r="I987" s="3"/>
+    </row>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H988" s="3"/>
+      <c r="I988" s="3"/>
+    </row>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H989" s="3"/>
+      <c r="I989" s="3"/>
+    </row>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H990" s="3"/>
+      <c r="I990" s="3"/>
+    </row>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H991" s="3"/>
+      <c r="I991" s="3"/>
+    </row>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H992" s="3"/>
+      <c r="I992" s="3"/>
+    </row>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H993" s="3"/>
+      <c r="I993" s="3"/>
+    </row>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H994" s="3"/>
+      <c r="I994" s="3"/>
+    </row>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H995" s="3"/>
+      <c r="I995" s="3"/>
+    </row>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H996" s="3"/>
+      <c r="I996" s="3"/>
+    </row>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H997" s="3"/>
+      <c r="I997" s="3"/>
+    </row>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H998" s="3"/>
+      <c r="I998" s="3"/>
+    </row>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H999" s="3"/>
+      <c r="I999" s="3"/>
+    </row>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1000" s="3"/>
+      <c r="I1000" s="3"/>
+    </row>
+    <row r="1001" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1001" s="3"/>
+      <c r="I1001" s="3"/>
+    </row>
+    <row r="1002" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1002" s="3"/>
+      <c r="I1002" s="3"/>
+    </row>
+    <row r="1003" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1003" s="3"/>
+      <c r="I1003" s="3"/>
+    </row>
+    <row r="1004" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1004" s="3"/>
+      <c r="I1004" s="3"/>
+    </row>
+    <row r="1005" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H1005" s="3"/>
+      <c r="I1005" s="3"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I1:I1005" type="list">
@@ -458,14 +4460,14 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -474,7 +4476,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -492,7 +4494,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1"/>
     </row>
@@ -501,13 +4503,13 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>20</v>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C6" s="1"/>
     </row>
